--- a/02 Базовые функции Репин Антон.xlsx
+++ b/02 Базовые функции Репин Антон.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FA12D26-D021-4AAF-9112-95BB52BB88EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="855" firstSheet="18" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13740" tabRatio="855"/>
   </bookViews>
   <sheets>
     <sheet name="ДАТА" sheetId="1" r:id="rId1"/>
@@ -39,7 +38,7 @@
     <sheet name="ИНДЕКС" sheetId="25" r:id="rId29"/>
     <sheet name="РАНГ" sheetId="26" r:id="rId30"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="405">
   <si>
     <t>tolstyakoff.ru</t>
   </si>
@@ -1456,11 +1455,14 @@
   <si>
     <t>//ошибки - не текст и не число</t>
   </si>
+  <si>
+    <t>Репин Антон Сергеевич</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
@@ -1472,7 +1474,7 @@
     <numFmt numFmtId="171" formatCode="#,##0.0"/>
     <numFmt numFmtId="172" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1612,8 +1614,17 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1641,6 +1652,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE25896"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1713,7 +1730,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1865,41 +1882,25 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Гиперссылка" xfId="2" builtinId="8"/>
-    <cellStyle name="Гиперссылка 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Гиперссылка 2" xfId="4"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Обычный 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2" xfId="3"/>
+    <cellStyle name="Обычный 3" xfId="5"/>
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1917,13 +1918,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1963,6 +1957,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1972,12 +1976,9 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1993,13 +1994,6 @@
         <b/>
         <i val="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -2030,8 +2024,8 @@
       <xdr:rowOff>168165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>572218</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>230184</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>168165</xdr:rowOff>
     </xdr:to>
@@ -2040,7 +2034,7 @@
         <xdr:cNvPr id="3" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2153,74 +2147,6 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>24055</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>2199</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>543792</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Скругленный прямоугольник 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24055" y="2199"/>
-          <a:ext cx="519737" cy="181374"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:blipFill dpi="0" rotWithShape="1">
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:srcRect/>
-          <a:tile tx="0" ty="0" sx="30000" sy="30000" flip="none" algn="tl"/>
-        </a:blipFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="ru-RU" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2244,7 +2170,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0900-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2435,7 +2361,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0900-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2508,7 +2434,7 @@
         <xdr:cNvPr id="2" name="Группа 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2527,7 +2453,7 @@
           <xdr:cNvPr id="3" name="TextBox 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000003000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000003000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2580,7 +2506,7 @@
           <xdr:cNvPr id="4" name="TextBox 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000004000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000004000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2651,7 +2577,7 @@
         <xdr:cNvPr id="5" name="Группа 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000005000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2670,7 +2596,7 @@
           <xdr:cNvPr id="6" name="TextBox 5">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000006000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000006000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2723,7 +2649,7 @@
           <xdr:cNvPr id="7" name="TextBox 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000007000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000007000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2794,7 +2720,7 @@
         <xdr:cNvPr id="8" name="Группа 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000008000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2813,7 +2739,7 @@
           <xdr:cNvPr id="9" name="TextBox 8">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-000009000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-000009000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2866,7 +2792,7 @@
           <xdr:cNvPr id="10" name="TextBox 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-00000A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-00000A000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -2937,7 +2863,7 @@
         <xdr:cNvPr id="11" name="TextBox 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-00000B000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3104,7 +3030,7 @@
         <xdr:cNvPr id="12" name="Скругленный прямоугольник 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0A00-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0A00-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3177,7 +3103,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0B00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0B00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3250,7 +3176,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0C00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3405,7 +3331,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0C00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3478,7 +3404,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0D00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0D00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3551,7 +3477,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0E00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0E00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3624,7 +3550,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0F00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0F00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3697,7 +3623,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3828,7 +3754,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3901,7 +3827,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3974,7 +3900,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4047,7 +3973,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4175,7 +4101,7 @@
         <xdr:cNvPr id="4" name="Скругленный прямоугольник 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4248,7 +4174,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4321,7 +4247,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4394,7 +4320,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1500-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4467,7 +4393,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4540,7 +4466,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4613,7 +4539,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1800-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4777,7 +4703,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1800-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1800-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4850,7 +4776,7 @@
         <xdr:cNvPr id="2" name="Группа 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4869,7 +4795,7 @@
           <xdr:cNvPr id="3" name="TextBox 2">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000003000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000003000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -4943,7 +4869,7 @@
           <xdr:cNvPr id="4" name="TextBox 3">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000004000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000004000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5017,7 +4943,7 @@
           <xdr:cNvPr id="5" name="Прямая со стрелкой 4">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000005000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000005000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5074,7 +5000,7 @@
         <xdr:cNvPr id="6" name="Группа 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000006000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5093,7 +5019,7 @@
           <xdr:cNvPr id="7" name="TextBox 6">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000007000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000007000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5150,7 +5076,7 @@
           <xdr:cNvPr id="8" name="Прямая со стрелкой 7">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000008000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000008000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5207,7 +5133,7 @@
         <xdr:cNvPr id="9" name="Группа 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-000009000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5226,7 +5152,7 @@
           <xdr:cNvPr id="10" name="TextBox 9">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-00000A000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-00000A000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5290,7 +5216,7 @@
           <xdr:cNvPr id="11" name="Прямая со стрелкой 10">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-00000B000000}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-00000B000000}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -5347,7 +5273,7 @@
         <xdr:cNvPr id="12" name="Скругленный прямоугольник 11">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1900-00000C000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1900-00000C000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5420,7 +5346,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1A00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1A00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5563,7 +5489,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1A00-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1A00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5636,7 +5562,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1B00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1B00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5725,7 +5651,7 @@
         <xdr:cNvPr id="3" name="Прямая со стрелкой 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1B00-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1B00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5781,7 +5707,7 @@
         <xdr:cNvPr id="4" name="Скругленный прямоугольник 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1B00-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1B00-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5854,7 +5780,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1C00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1C00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5947,7 +5873,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1C00-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1C00-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6020,7 +5946,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6093,7 +6019,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1D00-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1D00-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6236,7 +6162,7 @@
         <xdr:cNvPr id="4" name="Скругленный прямоугольник 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-1D00-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-1D00-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6309,7 +6235,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6382,7 +6308,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6455,7 +6381,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6528,7 +6454,7 @@
         <xdr:cNvPr id="2" name="Скругленный прямоугольник 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6601,7 +6527,7 @@
         <xdr:cNvPr id="2" name="Прямоугольник: скругленные углы 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6846,7 +6772,7 @@
         <xdr:cNvPr id="3" name="Скругленный прямоугольник 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0700-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6919,7 +6845,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0800-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7022,7 +6948,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0800-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7125,7 +7051,7 @@
         <xdr:cNvPr id="4" name="Скругленный прямоугольник 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000004000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0800-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7179,9 +7105,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7219,7 +7145,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -7291,7 +7217,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7464,31 +7390,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:I15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.28515625" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
     <col min="15" max="15" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="101" t="s">
+        <v>404</v>
+      </c>
       <c r="B1" s="96" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="2:9" ht="22.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" ht="22.5" x14ac:dyDescent="0.45">
       <c r="B2" s="95"/>
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="F4" s="86" t="s">
         <v>2</v>
       </c>
@@ -7502,7 +7431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F5" s="3">
         <v>1999</v>
       </c>
@@ -7517,7 +7446,7 @@
         <v>36161</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F6" s="3">
         <v>2000</v>
       </c>
@@ -7532,7 +7461,7 @@
         <v>36526</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F7" s="3">
         <v>2005</v>
       </c>
@@ -7547,7 +7476,7 @@
         <v>38395</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F8" s="3">
         <v>2010</v>
       </c>
@@ -7562,7 +7491,7 @@
         <v>40473</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F9" s="3">
         <v>2018</v>
       </c>
@@ -7577,7 +7506,7 @@
         <v>43269</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F10" s="3">
         <v>2022</v>
       </c>
@@ -7592,7 +7521,7 @@
         <v>44788</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F11" s="3">
         <v>2026</v>
       </c>
@@ -7607,7 +7536,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F12" s="3">
         <v>2030</v>
       </c>
@@ -7622,7 +7551,7 @@
         <v>47847</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F13" s="3">
         <v>2045</v>
       </c>
@@ -7637,7 +7566,7 @@
         <v>53049</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F14" s="3">
         <v>2050</v>
       </c>
@@ -7652,7 +7581,7 @@
         <v>54972</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F15" s="3">
         <v>2099</v>
       </c>
@@ -7674,7 +7603,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7881,7 +7810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7938,7 +7867,7 @@
         <v>118</v>
       </c>
       <c r="H5" s="49">
-        <f>SUMIF(B:B, G5, D:D)</f>
+        <f>SUMIF(B:B, G5,D:D )</f>
         <v>33000</v>
       </c>
       <c r="K5" s="2"/>
@@ -8045,7 +7974,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8109,7 +8038,7 @@
         <v>233</v>
       </c>
       <c r="H5" s="53">
-        <f>AVERAGEIF(C:C, "&gt;5000", C:C)</f>
+        <f>AVERAGEIF(C:C, "&gt;5000",C:C )</f>
         <v>6733.333333333333</v>
       </c>
     </row>
@@ -8151,7 +8080,7 @@
         <v>237</v>
       </c>
       <c r="H7" s="53">
-        <f>AVERAGEIF(D:D, "Да", C:C)</f>
+        <f>AVERAGEIF(D:D, "Да",C:C )</f>
         <v>6125</v>
       </c>
     </row>
@@ -8251,7 +8180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8281,7 +8210,7 @@
       <c r="C4" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="E4" s="99" t="s">
         <v>149</v>
       </c>
     </row>
@@ -8292,7 +8221,7 @@
       <c r="C5" s="3">
         <v>58</v>
       </c>
-      <c r="E5" s="98"/>
+      <c r="E5" s="100"/>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -8326,7 +8255,7 @@
       <c r="C8" s="3">
         <v>96</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="99" t="s">
         <v>154</v>
       </c>
       <c r="F8" s="2"/>
@@ -8339,7 +8268,7 @@
       <c r="C9" s="3">
         <v>84</v>
       </c>
-      <c r="E9" s="98"/>
+      <c r="E9" s="100"/>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
@@ -8416,7 +8345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8515,7 +8444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8768,7 +8697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8871,7 +8800,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9020,7 +8949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9170,7 +9099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9335,7 +9264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9561,7 +9490,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9720,7 +9649,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9935,7 +9864,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10172,7 +10101,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:D15">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10182,7 +10111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10204,7 +10133,7 @@
       <c r="B4" s="87" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="97" t="s">
+      <c r="D4" s="99" t="s">
         <v>270</v>
       </c>
     </row>
@@ -10212,7 +10141,7 @@
       <c r="B5" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D5" s="98"/>
+      <c r="D5" s="100"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -10310,7 +10239,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10565,13 +10494,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:E14">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Истина">
       <formula>NOT(ISERROR(SEARCH("Истина",C5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="Ложь">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Ложь">
       <formula>NOT(ISERROR(SEARCH("Ложь",C5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10581,7 +10510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10613,10 +10542,10 @@
       <c r="C4" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="E4" s="97" t="s">
+      <c r="E4" s="99" t="s">
         <v>266</v>
       </c>
-      <c r="F4" s="97" t="s">
+      <c r="F4" s="99" t="s">
         <v>267</v>
       </c>
     </row>
@@ -10627,8 +10556,8 @@
       <c r="C5" s="3">
         <v>58</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -10710,10 +10639,10 @@
         <v>70</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="97" t="s">
+      <c r="E11" s="99" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="99" t="s">
         <v>268</v>
       </c>
     </row>
@@ -10726,8 +10655,8 @@
         <v>24</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -10792,7 +10721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11033,7 +10962,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11080,7 +11009,7 @@
         <f>B5/C5</f>
         <v>1900</v>
       </c>
-      <c r="E5" s="100">
+      <c r="E5" s="98">
         <f>IFERROR(D5,0)</f>
         <v>1900</v>
       </c>
@@ -11096,7 +11025,7 @@
         <f t="shared" ref="D6:D15" si="0">B6/C6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E6" s="100">
+      <c r="E6" s="98">
         <f t="shared" ref="E6:E15" si="1">IFERROR(D6,0)</f>
         <v>0</v>
       </c>
@@ -11112,7 +11041,7 @@
         <f t="shared" si="0"/>
         <v>1960</v>
       </c>
-      <c r="E7" s="100">
+      <c r="E7" s="98">
         <f t="shared" si="1"/>
         <v>1960</v>
       </c>
@@ -11128,7 +11057,7 @@
         <f t="shared" si="0"/>
         <v>730</v>
       </c>
-      <c r="E8" s="100">
+      <c r="E8" s="98">
         <f t="shared" si="1"/>
         <v>730</v>
       </c>
@@ -11144,7 +11073,7 @@
         <f t="shared" si="0"/>
         <v>2383.3333333333335</v>
       </c>
-      <c r="E9" s="100">
+      <c r="E9" s="98">
         <f t="shared" si="1"/>
         <v>2383.3333333333335</v>
       </c>
@@ -11160,7 +11089,7 @@
         <f t="shared" si="0"/>
         <v>1385.7142857142858</v>
       </c>
-      <c r="E10" s="100">
+      <c r="E10" s="98">
         <f t="shared" si="1"/>
         <v>1385.7142857142858</v>
       </c>
@@ -11176,7 +11105,7 @@
         <f t="shared" si="0"/>
         <v>550</v>
       </c>
-      <c r="E11" s="100">
+      <c r="E11" s="98">
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
@@ -11192,7 +11121,7 @@
         <f t="shared" si="0"/>
         <v>366.66666666666669</v>
       </c>
-      <c r="E12" s="100">
+      <c r="E12" s="98">
         <f t="shared" si="1"/>
         <v>366.66666666666669</v>
       </c>
@@ -11208,7 +11137,7 @@
         <f t="shared" si="0"/>
         <v>855.55555555555554</v>
       </c>
-      <c r="E13" s="100">
+      <c r="E13" s="98">
         <f t="shared" si="1"/>
         <v>855.55555555555554</v>
       </c>
@@ -11224,7 +11153,7 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="E14" s="100">
+      <c r="E14" s="98">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -11240,7 +11169,7 @@
         <f t="shared" si="0"/>
         <v>1785.7142857142858</v>
       </c>
-      <c r="E15" s="100">
+      <c r="E15" s="98">
         <f t="shared" si="1"/>
         <v>1785.7142857142858</v>
       </c>
@@ -11255,7 +11184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11407,7 +11336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11677,7 +11606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:H22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11703,7 +11632,7 @@
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <f ca="1">TODAY()</f>
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="C5" s="79" t="s">
         <v>339</v>
@@ -11716,7 +11645,7 @@
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <f ca="1">TODAY()-7</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="C6" s="79" t="s">
         <v>341</v>
@@ -11729,7 +11658,7 @@
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <f ca="1">TODAY()+7</f>
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C7" s="79" t="s">
         <v>343</v>
@@ -11742,7 +11671,7 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <f ca="1">TODAY()+90</f>
-        <v>46365</v>
+        <v>46366</v>
       </c>
       <c r="C8" s="79" t="s">
         <v>345</v>
@@ -11755,7 +11684,7 @@
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <f ca="1">EDATE(TODAY(), 3)</f>
-        <v>46366</v>
+        <v>46367</v>
       </c>
       <c r="C9" s="79" t="s">
         <v>347</v>
@@ -11768,7 +11697,7 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <f ca="1">EDATE(TODAY(), 12)</f>
-        <v>46640</v>
+        <v>46641</v>
       </c>
       <c r="C10" s="79" t="s">
         <v>349</v>
@@ -11781,7 +11710,7 @@
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <f ca="1">EDATE(TODAY(), -12)</f>
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="C11" s="79" t="s">
         <v>351</v>
@@ -11820,7 +11749,7 @@
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="80">
         <f ca="1">TODAY()+TIME( 18, 0, 0 )</f>
-        <v>46275.75</v>
+        <v>46276.75</v>
       </c>
       <c r="C14" s="81" t="s">
         <v>357</v>
@@ -11832,7 +11761,7 @@
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="80">
         <f ca="1">TODAY()+1+TIME(12,0, 0)</f>
-        <v>46276.5</v>
+        <v>46277.5</v>
       </c>
       <c r="C15" s="81" t="s">
         <v>359</v>
@@ -11857,7 +11786,7 @@
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <f ca="1">NOW()</f>
-        <v>46275.979404513891</v>
+        <v>46276.390718402778</v>
       </c>
       <c r="C21" s="84" t="s">
         <v>377</v>
@@ -11876,7 +11805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12105,7 +12034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12330,7 +12259,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12668,7 +12597,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:K13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12951,7 +12880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J14"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13222,7 +13151,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13259,7 +13188,7 @@
       <c r="C5" s="41">
         <v>110000</v>
       </c>
-      <c r="D5" s="99" t="str">
+      <c r="D5" s="97" t="str">
         <f>IF(C5&gt;=90000, "Да", "Нет")</f>
         <v>Да</v>
       </c>
@@ -13406,7 +13335,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5:D15">
-    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Да">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="Да">
       <formula>NOT(ISERROR(SEARCH("Да",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13416,7 +13345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13652,26 +13581,26 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C14">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Ложь">
       <formula>NOT(ISERROR(SEARCH("Ложь",F5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Истина">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Истина">
       <formula>NOT(ISERROR(SEARCH("Истина",F5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Истина">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Истина">
       <formula>NOT(ISERROR(SEARCH("Истина",C1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Ложь">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Ложь">
       <formula>NOT(ISERROR(SEARCH("Ложь",C1)))</formula>
     </cfRule>
   </conditionalFormatting>
